--- a/data/datasets/features/cleaned_feature_group_2.xlsx
+++ b/data/datasets/features/cleaned_feature_group_2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,45 +440,65 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>pca_g_production_index[t-1]</t>
+          <t>mean_g_production_index[t]</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>mean_g_production_index[t-1]</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>g_retail_nonfood[t]</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>g_retail_nonfood[t-1]</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>g_real_salary[t]</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>g_real_salary[t-1]</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>unemployment_rate[t]</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>unemployment_rate_diff[t]</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>g_household_loans[t]</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>g_household_loans[t-1]</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>consumer_confidence[t]</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>consumer_confidence[t-1]</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>consumer_confidence[t-2]</t>
         </is>
@@ -491,21 +511,31 @@
       <c r="B2" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="n">
+        <v>0.04650208407981249</v>
+      </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>0.3001910841757038</v>
+        <v>0.182878994903372</v>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="n">
+        <v>0.3001910841757038</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="n">
         <v>0.048</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>42</v>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -515,26 +545,38 @@
         <v>43496</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1064349690258858</v>
+        <v>-0.214354797390349</v>
       </c>
       <c r="D3" t="n">
+        <v>0.04650208407981249</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-0.248777840248084</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.182878994903372</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>-0.2407300599278142</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>0.3001910841757038</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.049</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="N3" t="n">
+        <v>42</v>
+      </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -544,28 +586,40 @@
         <v>43524</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.5064615186595358</v>
+        <v>0.1124224503070768</v>
       </c>
       <c r="D4" t="n">
+        <v>-0.214354797390349</v>
+      </c>
+      <c r="E4" t="n">
+        <v>-0.02496083683519168</v>
+      </c>
+      <c r="F4" t="n">
         <v>-0.248777840248084</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>0.01444188127193846</v>
       </c>
-      <c r="F4" t="n">
+      <c r="H4" t="n">
         <v>-0.2407300599278142</v>
       </c>
-      <c r="G4" t="n">
+      <c r="I4" t="n">
         <v>0.049</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>0.09043772350511459</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="n">
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="N4" t="n">
+        <v>34.40000000000001</v>
+      </c>
+      <c r="O4" t="n">
         <v>42</v>
       </c>
     </row>
@@ -577,30 +631,42 @@
         <v>43555</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3895631711375039</v>
+        <v>0.1122700945964041</v>
       </c>
       <c r="D5" t="n">
+        <v>0.1124224503070768</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0.09525627462071751</v>
+      </c>
+      <c r="F5" t="n">
         <v>-0.02496083683519168</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>0.07231981897397022</v>
       </c>
-      <c r="F5" t="n">
+      <c r="H5" t="n">
         <v>0.01444188127193846</v>
       </c>
-      <c r="G5" t="n">
+      <c r="I5" t="n">
         <v>0.047</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>-0.002000000000000002</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>0.135749615613026</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.09043772350511459</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="N5" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="O5" t="n">
         <v>34.40000000000001</v>
       </c>
     </row>
@@ -612,30 +678,42 @@
         <v>43585</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1597762779982141</v>
+        <v>-0.1153626954404132</v>
       </c>
       <c r="D6" t="n">
+        <v>0.1122700945964041</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-0.007863716650431618</v>
+      </c>
+      <c r="F6" t="n">
         <v>0.09525627462071751</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>0.03382945696147943</v>
       </c>
-      <c r="F6" t="n">
+      <c r="H6" t="n">
         <v>0.07231981897397022</v>
       </c>
-      <c r="G6" t="n">
+      <c r="I6" t="n">
         <v>0.047</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>0.07981892382158118</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.135749615613026</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="N6" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="O6" t="n">
         <v>37.2</v>
       </c>
     </row>
@@ -647,30 +725,42 @@
         <v>43616</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.1788361075833125</v>
+        <v>-0.01457769599898917</v>
       </c>
       <c r="D7" t="n">
+        <v>-0.1153626954404132</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.01121476519777276</v>
+      </c>
+      <c r="F7" t="n">
         <v>-0.007863716650431618</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>-0.005546455397474115</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>0.03382945696147943</v>
       </c>
-      <c r="G7" t="n">
+      <c r="I7" t="n">
         <v>0.045</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>-0.002000000000000002</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>-0.1057929099372651</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.07981892382158118</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="N7" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O7" t="n">
         <v>37.2</v>
       </c>
     </row>
@@ -682,30 +772,42 @@
         <v>43646</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.05266087948014986</v>
+        <v>0.03665426897304358</v>
       </c>
       <c r="D8" t="n">
+        <v>-0.01457769599898917</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.02913755364560267</v>
+      </c>
+      <c r="F8" t="n">
         <v>0.01121476519777276</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>0.02925903877901304</v>
       </c>
-      <c r="F8" t="n">
+      <c r="H8" t="n">
         <v>-0.005546455397474115</v>
       </c>
-      <c r="G8" t="n">
+      <c r="I8" t="n">
         <v>0.044</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>0.03660297263539736</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>-0.1057929099372651</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="N8" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="O8" t="n">
         <v>36.8</v>
       </c>
     </row>
@@ -717,30 +819,42 @@
         <v>43677</v>
       </c>
       <c r="C9" t="n">
-        <v>0.08621235688255367</v>
+        <v>0.03600805362573412</v>
       </c>
       <c r="D9" t="n">
+        <v>0.03665426897304358</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.03106319731419216</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.02913755364560267</v>
       </c>
-      <c r="E9" t="n">
+      <c r="G9" t="n">
         <v>-0.05941137098422122</v>
       </c>
-      <c r="F9" t="n">
+      <c r="H9" t="n">
         <v>0.02925903877901304</v>
       </c>
-      <c r="G9" t="n">
+      <c r="I9" t="n">
         <v>0.045</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>0.06898670824421615</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.03660297263539736</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
+        <v>36</v>
+      </c>
+      <c r="N9" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O9" t="n">
         <v>37.6</v>
       </c>
     </row>
@@ -752,30 +866,42 @@
         <v>43708</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.005513651361484783</v>
+        <v>-0.007053318647906259</v>
       </c>
       <c r="D10" t="n">
+        <v>0.03600805362573412</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.04906122272754332</v>
+      </c>
+      <c r="F10" t="n">
         <v>0.03106319731419216</v>
       </c>
-      <c r="E10" t="n">
+      <c r="G10" t="n">
         <v>-0.03095818017166241</v>
       </c>
-      <c r="F10" t="n">
+      <c r="H10" t="n">
         <v>-0.05941137098422122</v>
       </c>
-      <c r="G10" t="n">
+      <c r="I10" t="n">
         <v>0.043</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>-0.002000000000000002</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>0.02843856900903075</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.06898670824421615</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="N10" t="n">
+        <v>36</v>
+      </c>
+      <c r="O10" t="n">
         <v>36.8</v>
       </c>
     </row>
@@ -787,30 +913,42 @@
         <v>43738</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.01095755655977734</v>
+        <v>0.0001137142721336915</v>
       </c>
       <c r="D11" t="n">
+        <v>-0.007053318647906259</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.01698925010386354</v>
+      </c>
+      <c r="F11" t="n">
         <v>0.04906122272754332</v>
       </c>
-      <c r="E11" t="n">
+      <c r="G11" t="n">
         <v>0.0145233062386263</v>
       </c>
-      <c r="F11" t="n">
+      <c r="H11" t="n">
         <v>-0.03095818017166241</v>
       </c>
-      <c r="G11" t="n">
+      <c r="I11" t="n">
         <v>0.045</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.002000000000000002</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>0.02221450150811588</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.02843856900903075</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
+        <v>36.40000000000001</v>
+      </c>
+      <c r="N11" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="O11" t="n">
         <v>36</v>
       </c>
     </row>
@@ -822,30 +960,42 @@
         <v>43769</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.007607601529729332</v>
+        <v>0.05695466271815164</v>
       </c>
       <c r="D12" t="n">
+        <v>0.0001137142721336915</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.01093027021444049</v>
+      </c>
+      <c r="F12" t="n">
         <v>-0.01698925010386354</v>
       </c>
-      <c r="E12" t="n">
+      <c r="G12" t="n">
         <v>0.020806852411555</v>
       </c>
-      <c r="F12" t="n">
+      <c r="H12" t="n">
         <v>0.0145233062386263</v>
       </c>
-      <c r="G12" t="n">
+      <c r="I12" t="n">
         <v>0.046</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>0.01146046505704357</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.02221450150811588</v>
       </c>
-      <c r="K12" t="n">
+      <c r="M12" t="n">
+        <v>38</v>
+      </c>
+      <c r="N12" t="n">
+        <v>36.40000000000001</v>
+      </c>
+      <c r="O12" t="n">
         <v>39.2</v>
       </c>
     </row>
@@ -857,30 +1007,42 @@
         <v>43799</v>
       </c>
       <c r="C13" t="n">
-        <v>0.06857073204740986</v>
+        <v>-0.06799413656042308</v>
       </c>
       <c r="D13" t="n">
+        <v>0.05695466271815164</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.007553922951293535</v>
+      </c>
+      <c r="F13" t="n">
         <v>0.01093027021444049</v>
       </c>
-      <c r="E13" t="n">
+      <c r="G13" t="n">
         <v>-0.008447789185832777</v>
       </c>
-      <c r="F13" t="n">
+      <c r="H13" t="n">
         <v>0.020806852411555</v>
       </c>
-      <c r="G13" t="n">
+      <c r="I13" t="n">
         <v>0.046</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>-0.02482220667544388</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.01146046505704357</v>
       </c>
-      <c r="K13" t="n">
+      <c r="M13" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="N13" t="n">
+        <v>38</v>
+      </c>
+      <c r="O13" t="n">
         <v>36.40000000000001</v>
       </c>
     </row>
@@ -892,30 +1054,42 @@
         <v>43830</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.142847770653575</v>
+        <v>0.0682282816761397</v>
       </c>
       <c r="D14" t="n">
+        <v>-0.06799413656042308</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.1669936195243826</v>
+      </c>
+      <c r="F14" t="n">
         <v>0.007553922951293535</v>
       </c>
-      <c r="E14" t="n">
+      <c r="G14" t="n">
         <v>0.339866983343059</v>
       </c>
-      <c r="F14" t="n">
+      <c r="H14" t="n">
         <v>-0.008447789185832777</v>
       </c>
-      <c r="G14" t="n">
+      <c r="I14" t="n">
         <v>0.046</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>0.1700098856093772</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>-0.02482220667544388</v>
       </c>
-      <c r="K14" t="n">
+      <c r="M14" t="n">
+        <v>42</v>
+      </c>
+      <c r="N14" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="O14" t="n">
         <v>38</v>
       </c>
     </row>
@@ -927,30 +1101,42 @@
         <v>43861</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1873719876101732</v>
+        <v>-0.2035507052286574</v>
       </c>
       <c r="D15" t="n">
+        <v>0.0682282816761397</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-0.2403419401519732</v>
+      </c>
+      <c r="F15" t="n">
         <v>0.1669936195243826</v>
       </c>
-      <c r="E15" t="n">
+      <c r="G15" t="n">
         <v>-0.2530720639990209</v>
       </c>
-      <c r="F15" t="n">
+      <c r="H15" t="n">
         <v>0.339866983343059</v>
       </c>
-      <c r="G15" t="n">
+      <c r="I15" t="n">
         <v>0.047</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>-0.2721445780140939</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.1700098856093772</v>
       </c>
-      <c r="K15" t="n">
+      <c r="M15" t="n">
+        <v>36</v>
+      </c>
+      <c r="N15" t="n">
+        <v>42</v>
+      </c>
+      <c r="O15" t="n">
         <v>39.6</v>
       </c>
     </row>
@@ -962,30 +1148,42 @@
         <v>43890</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.5013560472043319</v>
+        <v>0.1289762564995425</v>
       </c>
       <c r="D16" t="n">
+        <v>-0.2035507052286574</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-0.007935298931046053</v>
+      </c>
+      <c r="F16" t="n">
         <v>-0.2403419401519732</v>
       </c>
-      <c r="E16" t="n">
+      <c r="G16" t="n">
         <v>0.009160664096522053</v>
       </c>
-      <c r="F16" t="n">
+      <c r="H16" t="n">
         <v>-0.2530720639990209</v>
       </c>
-      <c r="G16" t="n">
+      <c r="I16" t="n">
         <v>0.046</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>0.1111933431822296</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>-0.2721445780140939</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="N16" t="n">
+        <v>36</v>
+      </c>
+      <c r="O16" t="n">
         <v>42</v>
       </c>
     </row>
@@ -997,30 +1195,42 @@
         <v>43921</v>
       </c>
       <c r="C17" t="n">
-        <v>0.4046900669732068</v>
+        <v>0.04414726217830389</v>
       </c>
       <c r="D17" t="n">
+        <v>0.1289762564995425</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.1222948968521445</v>
+      </c>
+      <c r="F17" t="n">
         <v>-0.007935298931046053</v>
       </c>
-      <c r="E17" t="n">
+      <c r="G17" t="n">
         <v>0.07220768874224115</v>
       </c>
-      <c r="F17" t="n">
+      <c r="H17" t="n">
         <v>0.009160664096522053</v>
       </c>
-      <c r="G17" t="n">
+      <c r="I17" t="n">
         <v>0.047</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>0.1933108707943501</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.1111933431822296</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
+        <v>32.40000000000001</v>
+      </c>
+      <c r="N17" t="n">
+        <v>36.8</v>
+      </c>
+      <c r="O17" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1032,30 +1242,42 @@
         <v>43951</v>
       </c>
       <c r="C18" t="n">
-        <v>0.04975714368599229</v>
+        <v>-0.130877945322883</v>
       </c>
       <c r="D18" t="n">
+        <v>0.04414726217830389</v>
+      </c>
+      <c r="E18" t="n">
+        <v>-0.3990030020419976</v>
+      </c>
+      <c r="F18" t="n">
         <v>0.1222948968521445</v>
       </c>
-      <c r="E18" t="n">
+      <c r="G18" t="n">
         <v>-0.04019531816985977</v>
       </c>
-      <c r="F18" t="n">
+      <c r="H18" t="n">
         <v>0.07220768874224115</v>
       </c>
-      <c r="G18" t="n">
+      <c r="I18" t="n">
         <v>0.058</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.011</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>-0.4603090547481274</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.1933108707943501</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
+        <v>24</v>
+      </c>
+      <c r="N18" t="n">
+        <v>32.40000000000001</v>
+      </c>
+      <c r="O18" t="n">
         <v>36.8</v>
       </c>
     </row>
@@ -1067,30 +1289,42 @@
         <v>43982</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.2712918777184584</v>
+        <v>0.01724085273721032</v>
       </c>
       <c r="D19" t="n">
+        <v>-0.130877945322883</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.1383385861117006</v>
+      </c>
+      <c r="F19" t="n">
         <v>-0.3990030020419976</v>
       </c>
-      <c r="E19" t="n">
+      <c r="G19" t="n">
         <v>0.02645422564122901</v>
       </c>
-      <c r="F19" t="n">
+      <c r="H19" t="n">
         <v>-0.04019531816985977</v>
       </c>
-      <c r="G19" t="n">
+      <c r="I19" t="n">
         <v>0.061</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.002999999999999996</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>0.1278050925000231</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>-0.4603090547481274</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="N19" t="n">
+        <v>24</v>
+      </c>
+      <c r="O19" t="n">
         <v>32.40000000000001</v>
       </c>
     </row>
@@ -1102,30 +1336,42 @@
         <v>44012</v>
       </c>
       <c r="C20" t="n">
-        <v>0.1135131172444329</v>
+        <v>0.06054001458665659</v>
       </c>
       <c r="D20" t="n">
+        <v>0.01724085273721032</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.2865851422194166</v>
+      </c>
+      <c r="F20" t="n">
         <v>0.1383385861117006</v>
       </c>
-      <c r="E20" t="n">
+      <c r="G20" t="n">
         <v>0.02486021088010371</v>
       </c>
-      <c r="F20" t="n">
+      <c r="H20" t="n">
         <v>0.02645422564122901</v>
       </c>
-      <c r="G20" t="n">
+      <c r="I20" t="n">
         <v>0.062</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>0.3579122373213293</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.1278050925000231</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="N20" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="O20" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1137,30 +1383,42 @@
         <v>44043</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0920927949150598</v>
+        <v>0.04745597146002067</v>
       </c>
       <c r="D21" t="n">
+        <v>0.06054001458665659</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.1280444754848344</v>
+      </c>
+      <c r="F21" t="n">
         <v>0.2865851422194166</v>
       </c>
-      <c r="E21" t="n">
+      <c r="G21" t="n">
         <v>-0.04130413380308551</v>
       </c>
-      <c r="F21" t="n">
+      <c r="H21" t="n">
         <v>0.02486021088010371</v>
       </c>
-      <c r="G21" t="n">
+      <c r="I21" t="n">
         <v>0.063</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>0.1688931314210811</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.3579122373213293</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
+        <v>32.40000000000001</v>
+      </c>
+      <c r="N21" t="n">
+        <v>28.8</v>
+      </c>
+      <c r="O21" t="n">
         <v>31.2</v>
       </c>
     </row>
@@ -1172,30 +1430,42 @@
         <v>44074</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00501869779468418</v>
+        <v>-0.0006044554444035732</v>
       </c>
       <c r="D22" t="n">
+        <v>0.04745597146002067</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.06440993956464092</v>
+      </c>
+      <c r="F22" t="n">
         <v>0.1280444754848344</v>
       </c>
-      <c r="E22" t="n">
+      <c r="G22" t="n">
         <v>-0.04939540877673221</v>
       </c>
-      <c r="F22" t="n">
+      <c r="H22" t="n">
         <v>-0.04130413380308551</v>
       </c>
-      <c r="G22" t="n">
+      <c r="I22" t="n">
         <v>0.064</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>0.06513624790476036</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.1688931314210811</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
+        <v>34</v>
+      </c>
+      <c r="N22" t="n">
+        <v>32.40000000000001</v>
+      </c>
+      <c r="O22" t="n">
         <v>28.8</v>
       </c>
     </row>
@@ -1207,30 +1477,42 @@
         <v>44104</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.005749651266149595</v>
+        <v>-0.007130594489971775</v>
       </c>
       <c r="D23" t="n">
+        <v>-0.0006044554444035732</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-0.02169179196687832</v>
+      </c>
+      <c r="F23" t="n">
         <v>0.06440993956464092</v>
       </c>
-      <c r="E23" t="n">
+      <c r="G23" t="n">
         <v>0.03451290591235212</v>
       </c>
-      <c r="F23" t="n">
+      <c r="H23" t="n">
         <v>-0.04939540877673221</v>
       </c>
-      <c r="G23" t="n">
+      <c r="I23" t="n">
         <v>0.063</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>0.06418228663893388</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.06513624790476036</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="N23" t="n">
+        <v>34</v>
+      </c>
+      <c r="O23" t="n">
         <v>32.40000000000001</v>
       </c>
     </row>
@@ -1242,30 +1524,42 @@
         <v>44135</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.0214050103546608</v>
+        <v>0.04650815365495342</v>
       </c>
       <c r="D24" t="n">
+        <v>-0.007130594489971775</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.02028310004671141</v>
+      </c>
+      <c r="F24" t="n">
         <v>-0.02169179196687832</v>
       </c>
-      <c r="E24" t="n">
+      <c r="G24" t="n">
         <v>0.00137831369448449</v>
       </c>
-      <c r="F24" t="n">
+      <c r="H24" t="n">
         <v>0.03451290591235212</v>
       </c>
-      <c r="G24" t="n">
+      <c r="I24" t="n">
         <v>0.063</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>0.02921921130187144</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.06418228663893388</v>
       </c>
-      <c r="K24" t="n">
+      <c r="M24" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="N24" t="n">
+        <v>37.6</v>
+      </c>
+      <c r="O24" t="n">
         <v>34</v>
       </c>
     </row>
@@ -1277,30 +1571,42 @@
         <v>44165</v>
       </c>
       <c r="C25" t="n">
-        <v>0.03835777846218298</v>
+        <v>-0.04429760171641628</v>
       </c>
       <c r="D25" t="n">
+        <v>0.04650815365495342</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-0.0112134260743223</v>
+      </c>
+      <c r="F25" t="n">
         <v>0.02028310004671141</v>
       </c>
-      <c r="E25" t="n">
+      <c r="G25" t="n">
         <v>-0.0123615537058851</v>
       </c>
-      <c r="F25" t="n">
+      <c r="H25" t="n">
         <v>0.00137831369448449</v>
       </c>
-      <c r="G25" t="n">
+      <c r="I25" t="n">
         <v>0.061</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>-0.002000000000000002</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>-0.007866861282766924</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.02921921130187144</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="N25" t="n">
+        <v>34.4</v>
+      </c>
+      <c r="O25" t="n">
         <v>37.6</v>
       </c>
     </row>
@@ -1312,30 +1618,42 @@
         <v>44196</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.06290834928730313</v>
+        <v>0.08652918834910528</v>
       </c>
       <c r="D26" t="n">
+        <v>-0.04429760171641628</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.1680075883547993</v>
+      </c>
+      <c r="F26" t="n">
         <v>-0.0112134260743223</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>0.3944012232665413</v>
       </c>
-      <c r="F26" t="n">
+      <c r="H26" t="n">
         <v>-0.0123615537058851</v>
       </c>
-      <c r="G26" t="n">
+      <c r="I26" t="n">
         <v>0.059</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>-0.002000000000000002</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>0.09574970521788306</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>-0.007866861282766924</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>37.2</v>
+      </c>
+      <c r="O26" t="n">
         <v>34.4</v>
       </c>
     </row>
@@ -1347,30 +1665,42 @@
         <v>44227</v>
       </c>
       <c r="C27" t="n">
-        <v>0.1930732173933881</v>
+        <v>-0.2777424017594374</v>
       </c>
       <c r="D27" t="n">
+        <v>0.08652918834910528</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-0.203825587986007</v>
+      </c>
+      <c r="F27" t="n">
         <v>0.1680075883547993</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>-0.2900134129193179</v>
       </c>
-      <c r="F27" t="n">
+      <c r="H27" t="n">
         <v>0.3944012232665413</v>
       </c>
-      <c r="G27" t="n">
+      <c r="I27" t="n">
         <v>0.058</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>-0.0009999999999999939</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>-0.3166810145718725</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.09574970521788306</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>32.8</v>
+      </c>
+      <c r="O27" t="n">
         <v>37.2</v>
       </c>
     </row>
@@ -1382,30 +1712,42 @@
         <v>44255</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.6638990959711595</v>
+        <v>0.1436914518727861</v>
       </c>
       <c r="D28" t="n">
+        <v>-0.2777424017594374</v>
+      </c>
+      <c r="E28" t="n">
+        <v>-0.0190414439792721</v>
+      </c>
+      <c r="F28" t="n">
         <v>-0.203825587986007</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>0.02658749595468946</v>
       </c>
-      <c r="F28" t="n">
+      <c r="H28" t="n">
         <v>-0.2900134129193179</v>
       </c>
-      <c r="G28" t="n">
+      <c r="I28" t="n">
         <v>0.057</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>0.1985096984828116</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>-0.3166810145718725</v>
       </c>
-      <c r="K28" t="n">
+      <c r="M28" t="n">
+        <v>36</v>
+      </c>
+      <c r="N28" t="n">
+        <v>35.2</v>
+      </c>
+      <c r="O28" t="n">
         <v>32.8</v>
       </c>
     </row>
@@ -1417,30 +1759,42 @@
         <v>44286</v>
       </c>
       <c r="C29" t="n">
-        <v>0.4624784506565406</v>
+        <v>0.1012707507055692</v>
       </c>
       <c r="D29" t="n">
+        <v>0.1436914518727861</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.1198586529507468</v>
+      </c>
+      <c r="F29" t="n">
         <v>-0.0190414439792721</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>0.07060485842920405</v>
       </c>
-      <c r="F29" t="n">
+      <c r="H29" t="n">
         <v>0.02658749595468946</v>
       </c>
-      <c r="G29" t="n">
+      <c r="I29" t="n">
         <v>0.054</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>-0.003000000000000003</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>0.2507591813945009</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.1985096984828116</v>
       </c>
-      <c r="K29" t="n">
+      <c r="M29" t="n">
+        <v>40</v>
+      </c>
+      <c r="N29" t="n">
+        <v>36</v>
+      </c>
+      <c r="O29" t="n">
         <v>35.2</v>
       </c>
     </row>
@@ -1452,30 +1806,42 @@
         <v>44316</v>
       </c>
       <c r="C30" t="n">
-        <v>0.1693209167185396</v>
+        <v>-0.1193275601628478</v>
       </c>
       <c r="D30" t="n">
+        <v>0.1012707507055692</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.01915409339613228</v>
+      </c>
+      <c r="F30" t="n">
         <v>0.1198586529507468</v>
       </c>
-      <c r="E30" t="n">
+      <c r="G30" t="n">
         <v>0.01955391089311331</v>
       </c>
-      <c r="F30" t="n">
+      <c r="H30" t="n">
         <v>0.07060485842920405</v>
       </c>
-      <c r="G30" t="n">
+      <c r="I30" t="n">
         <v>0.052</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>-0.002000000000000002</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>0.04952039748417936</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.2507591813945009</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
+        <v>38</v>
+      </c>
+      <c r="N30" t="n">
+        <v>40</v>
+      </c>
+      <c r="O30" t="n">
         <v>36</v>
       </c>
     </row>
@@ -1487,30 +1853,42 @@
         <v>44347</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.2193408066297849</v>
+        <v>-0.01381203440918988</v>
       </c>
       <c r="D31" t="n">
+        <v>-0.1193275601628478</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.01541693975070446</v>
+      </c>
+      <c r="F31" t="n">
         <v>0.01915409339613228</v>
       </c>
-      <c r="E31" t="n">
+      <c r="G31" t="n">
         <v>-0.01511308281833101</v>
       </c>
-      <c r="F31" t="n">
+      <c r="H31" t="n">
         <v>0.01955391089311331</v>
       </c>
-      <c r="G31" t="n">
+      <c r="I31" t="n">
         <v>0.049</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>-0.002999999999999996</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>-0.08419034991015706</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.04952039748417936</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="N31" t="n">
+        <v>38</v>
+      </c>
+      <c r="O31" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1522,30 +1900,42 @@
         <v>44377</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.03805749618267387</v>
+        <v>0.04448456682763013</v>
       </c>
       <c r="D32" t="n">
+        <v>-0.01381203440918988</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.01333062032731713</v>
+      </c>
+      <c r="F32" t="n">
         <v>0.01541693975070446</v>
       </c>
-      <c r="E32" t="n">
+      <c r="G32" t="n">
         <v>0.0393118091707958</v>
       </c>
-      <c r="F32" t="n">
+      <c r="H32" t="n">
         <v>-0.01511308281833101</v>
       </c>
-      <c r="G32" t="n">
+      <c r="I32" t="n">
         <v>0.048</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>0.1084462111271389</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>-0.08419034991015706</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
+        <v>36.40000000000001</v>
+      </c>
+      <c r="N32" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="O32" t="n">
         <v>38</v>
       </c>
     </row>
@@ -1557,30 +1947,42 @@
         <v>44408</v>
       </c>
       <c r="C33" t="n">
-        <v>0.09762528032526081</v>
+        <v>-0.008786856727728942</v>
       </c>
       <c r="D33" t="n">
+        <v>0.04448456682763013</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.03773968872912659</v>
+      </c>
+      <c r="F33" t="n">
         <v>0.01333062032731713</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>-0.06434790335119855</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>0.0393118091707958</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.045</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>-0.003000000000000003</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>-0.07636860962772618</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.1084462111271389</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="N33" t="n">
+        <v>36.40000000000001</v>
+      </c>
+      <c r="O33" t="n">
         <v>38.8</v>
       </c>
     </row>
@@ -1592,30 +1994,42 @@
         <v>44439</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0907799224671995</v>
+        <v>0.02430716457531523</v>
       </c>
       <c r="D34" t="n">
+        <v>-0.008786856727728942</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.06336683151228506</v>
+      </c>
+      <c r="F34" t="n">
         <v>0.03773968872912659</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>-0.0526346284363528</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>-0.06434790335119855</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.044</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>0.05258699354184659</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>-0.07636860962772618</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
+        <v>40</v>
+      </c>
+      <c r="N34" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="O34" t="n">
         <v>36.40000000000001</v>
       </c>
     </row>
@@ -1627,30 +2041,42 @@
         <v>44469</v>
       </c>
       <c r="C35" t="n">
-        <v>0.0571410386822856</v>
+        <v>0.03196233109057145</v>
       </c>
       <c r="D35" t="n">
+        <v>0.02430716457531523</v>
+      </c>
+      <c r="E35" t="n">
+        <v>-0.01474118534827629</v>
+      </c>
+      <c r="F35" t="n">
         <v>0.06336683151228506</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>0.0383121953979495</v>
       </c>
-      <c r="F35" t="n">
+      <c r="H35" t="n">
         <v>-0.0526346284363528</v>
       </c>
-      <c r="G35" t="n">
+      <c r="I35" t="n">
         <v>0.043</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>0.003187318452583909</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.05258699354184659</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="N35" t="n">
+        <v>40</v>
+      </c>
+      <c r="O35" t="n">
         <v>38.8</v>
       </c>
     </row>
@@ -1662,30 +2088,42 @@
         <v>44500</v>
       </c>
       <c r="C36" t="n">
-        <v>0.03977430920879065</v>
+        <v>0.02385323751424306</v>
       </c>
       <c r="D36" t="n">
+        <v>0.03196233109057145</v>
+      </c>
+      <c r="E36" t="n">
+        <v>-0.001038708545529232</v>
+      </c>
+      <c r="F36" t="n">
         <v>-0.01474118534827629</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>-0.01166537780228938</v>
       </c>
-      <c r="F36" t="n">
+      <c r="H36" t="n">
         <v>0.0383121953979495</v>
       </c>
-      <c r="G36" t="n">
+      <c r="I36" t="n">
         <v>0.043</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>-0.007955034900886782</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.003187318452583909</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
+        <v>38.40000000000001</v>
+      </c>
+      <c r="N36" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="O36" t="n">
         <v>40</v>
       </c>
     </row>
@@ -1697,30 +2135,42 @@
         <v>44530</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.001660629279499647</v>
+        <v>-0.04073992778466029</v>
       </c>
       <c r="D37" t="n">
+        <v>0.02385323751424306</v>
+      </c>
+      <c r="E37" t="n">
+        <v>-0.02256117160337845</v>
+      </c>
+      <c r="F37" t="n">
         <v>-0.001038708545529232</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>0.008434638007797313</v>
       </c>
-      <c r="F37" t="n">
+      <c r="H37" t="n">
         <v>-0.01166537780228938</v>
       </c>
-      <c r="G37" t="n">
+      <c r="I37" t="n">
         <v>0.043</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>0.0283263319827769</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>-0.007955034900886782</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="N37" t="n">
+        <v>38.40000000000001</v>
+      </c>
+      <c r="O37" t="n">
         <v>39.2</v>
       </c>
     </row>
@@ -1732,30 +2182,42 @@
         <v>44561</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.03835549652759056</v>
+        <v>0.08535345504486047</v>
       </c>
       <c r="D38" t="n">
+        <v>-0.04073992778466029</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.2130665304390789</v>
+      </c>
+      <c r="F38" t="n">
         <v>-0.02256117160337845</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>0.3903853567268287</v>
       </c>
-      <c r="F38" t="n">
+      <c r="H38" t="n">
         <v>0.008434638007797313</v>
       </c>
-      <c r="G38" t="n">
+      <c r="I38" t="n">
         <v>0.043</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>0.1182501936458382</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.0283263319827769</v>
       </c>
-      <c r="K38" t="n">
+      <c r="M38" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="N38" t="n">
+        <v>39.6</v>
+      </c>
+      <c r="O38" t="n">
         <v>38.40000000000001</v>
       </c>
     </row>
@@ -1767,30 +2229,42 @@
         <v>44592</v>
       </c>
       <c r="C39" t="n">
-        <v>0.1785944171857152</v>
+        <v>-0.2732737259394042</v>
       </c>
       <c r="D39" t="n">
+        <v>0.08535345504486047</v>
+      </c>
+      <c r="E39" t="n">
+        <v>-0.2111337208638872</v>
+      </c>
+      <c r="F39" t="n">
         <v>0.2130665304390789</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>-0.2926275227454778</v>
       </c>
-      <c r="F39" t="n">
+      <c r="H39" t="n">
         <v>0.3903853567268287</v>
       </c>
-      <c r="G39" t="n">
+      <c r="I39" t="n">
         <v>0.044</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>-0.2944404468086538</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.1182501936458382</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="N39" t="n">
+        <v>41.2</v>
+      </c>
+      <c r="O39" t="n">
         <v>39.6</v>
       </c>
     </row>
@@ -1802,30 +2276,42 @@
         <v>44620</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.6483538797094176</v>
+        <v>0.131247954729719</v>
       </c>
       <c r="D40" t="n">
+        <v>-0.2732737259394042</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.01345886111124428</v>
+      </c>
+      <c r="F40" t="n">
         <v>-0.2111337208638872</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>0.0172987461528622</v>
       </c>
-      <c r="F40" t="n">
+      <c r="H40" t="n">
         <v>-0.2926275227454778</v>
       </c>
-      <c r="G40" t="n">
+      <c r="I40" t="n">
         <v>0.041</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>-0.002999999999999996</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>0.1729335849632088</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>-0.2944404468086538</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="N40" t="n">
+        <v>35.6</v>
+      </c>
+      <c r="O40" t="n">
         <v>41.2</v>
       </c>
     </row>
@@ -1837,30 +2323,42 @@
         <v>44651</v>
       </c>
       <c r="C41" t="n">
-        <v>0.4363012784912341</v>
+        <v>0.1222469896870073</v>
       </c>
       <c r="D41" t="n">
+        <v>0.131247954729719</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.1315541010599746</v>
+      </c>
+      <c r="F41" t="n">
         <v>0.01345886111124428</v>
       </c>
-      <c r="E41" t="n">
+      <c r="G41" t="n">
         <v>0.08182296541246847</v>
       </c>
-      <c r="F41" t="n">
+      <c r="H41" t="n">
         <v>0.0172987461528622</v>
       </c>
-      <c r="G41" t="n">
+      <c r="I41" t="n">
         <v>0.041</v>
       </c>
-      <c r="H41" t="n">
+      <c r="J41" t="n">
         <v>0</v>
       </c>
-      <c r="I41" t="n">
+      <c r="K41" t="n">
         <v>-0.221605344220827</v>
       </c>
-      <c r="J41" t="n">
+      <c r="L41" t="n">
         <v>0.1729335849632088</v>
       </c>
-      <c r="K41" t="n">
+      <c r="M41" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="N41" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="O41" t="n">
         <v>35.6</v>
       </c>
     </row>
@@ -1872,30 +2370,42 @@
         <v>44681</v>
       </c>
       <c r="C42" t="n">
-        <v>0.1579093090070217</v>
+        <v>-0.1977363360664131</v>
       </c>
       <c r="D42" t="n">
+        <v>0.1222469896870073</v>
+      </c>
+      <c r="E42" t="n">
+        <v>-0.159163722933409</v>
+      </c>
+      <c r="F42" t="n">
         <v>0.1315541010599746</v>
       </c>
-      <c r="E42" t="n">
+      <c r="G42" t="n">
         <v>-0.08155662153795795</v>
       </c>
-      <c r="F42" t="n">
+      <c r="H42" t="n">
         <v>0.08182296541246847</v>
       </c>
-      <c r="G42" t="n">
+      <c r="I42" t="n">
         <v>0.04</v>
       </c>
-      <c r="H42" t="n">
+      <c r="J42" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I42" t="n">
+      <c r="K42" t="n">
         <v>-0.3395966127882456</v>
       </c>
-      <c r="J42" t="n">
+      <c r="L42" t="n">
         <v>-0.221605344220827</v>
       </c>
-      <c r="K42" t="n">
+      <c r="M42" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="N42" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O42" t="n">
         <v>34.8</v>
       </c>
     </row>
@@ -1907,30 +2417,42 @@
         <v>44712</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.3134858995304597</v>
+        <v>0.0721523021912498</v>
       </c>
       <c r="D43" t="n">
+        <v>-0.1977363360664131</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.005745791108402232</v>
+      </c>
+      <c r="F43" t="n">
         <v>-0.159163722933409</v>
       </c>
-      <c r="E43" t="n">
+      <c r="G43" t="n">
         <v>0.001816978436841143</v>
       </c>
-      <c r="F43" t="n">
+      <c r="H43" t="n">
         <v>-0.08155662153795795</v>
       </c>
-      <c r="G43" t="n">
+      <c r="I43" t="n">
         <v>0.039</v>
       </c>
-      <c r="H43" t="n">
+      <c r="J43" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I43" t="n">
+      <c r="K43" t="n">
         <v>0.1643959667129613</v>
       </c>
-      <c r="J43" t="n">
+      <c r="L43" t="n">
         <v>-0.3395966127882456</v>
       </c>
-      <c r="K43" t="n">
+      <c r="M43" t="n">
+        <v>27.20073750435151</v>
+      </c>
+      <c r="N43" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="O43" t="n">
         <v>25.6</v>
       </c>
     </row>
@@ -1942,30 +2464,42 @@
         <v>44742</v>
       </c>
       <c r="C44" t="n">
-        <v>0.1042595124747944</v>
+        <v>-0.008929648334551565</v>
       </c>
       <c r="D44" t="n">
+        <v>0.0721523021912498</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.01449929333732247</v>
+      </c>
+      <c r="F44" t="n">
         <v>0.005745791108402232</v>
       </c>
-      <c r="E44" t="n">
+      <c r="G44" t="n">
         <v>0.06962903071392401</v>
       </c>
-      <c r="F44" t="n">
+      <c r="H44" t="n">
         <v>0.001816978436841143</v>
       </c>
-      <c r="G44" t="n">
+      <c r="I44" t="n">
         <v>0.039</v>
       </c>
-      <c r="H44" t="n">
+      <c r="J44" t="n">
         <v>0</v>
       </c>
-      <c r="I44" t="n">
+      <c r="K44" t="n">
         <v>0.3067568248993429</v>
       </c>
-      <c r="J44" t="n">
+      <c r="L44" t="n">
         <v>0.1643959667129613</v>
       </c>
-      <c r="K44" t="n">
+      <c r="M44" t="n">
+        <v>29.61332618959294</v>
+      </c>
+      <c r="N44" t="n">
+        <v>27.20073750435151</v>
+      </c>
+      <c r="O44" t="n">
         <v>25.6</v>
       </c>
     </row>
@@ -1977,30 +2511,42 @@
         <v>44773</v>
       </c>
       <c r="C45" t="n">
-        <v>0.003457140166087288</v>
+        <v>0.04070595256760523</v>
       </c>
       <c r="D45" t="n">
+        <v>-0.008929648334551565</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.03002672334210166</v>
+      </c>
+      <c r="F45" t="n">
         <v>0.01449929333732247</v>
       </c>
-      <c r="E45" t="n">
+      <c r="G45" t="n">
         <v>-0.06201511497194401</v>
       </c>
-      <c r="F45" t="n">
+      <c r="H45" t="n">
         <v>0.06962903071392401</v>
       </c>
-      <c r="G45" t="n">
+      <c r="I45" t="n">
         <v>0.039</v>
       </c>
-      <c r="H45" t="n">
+      <c r="J45" t="n">
         <v>0</v>
       </c>
-      <c r="I45" t="n">
+      <c r="K45" t="n">
         <v>0.1045171306043</v>
       </c>
-      <c r="J45" t="n">
+      <c r="L45" t="n">
         <v>0.3067568248993429</v>
       </c>
-      <c r="K45" t="n">
+      <c r="M45" t="n">
+        <v>34.41543826978847</v>
+      </c>
+      <c r="N45" t="n">
+        <v>29.61332618959294</v>
+      </c>
+      <c r="O45" t="n">
         <v>27.20073750435151</v>
       </c>
     </row>
@@ -2012,30 +2558,42 @@
         <v>44804</v>
       </c>
       <c r="C46" t="n">
-        <v>0.01890998246585104</v>
+        <v>0.03579798985912208</v>
       </c>
       <c r="D46" t="n">
+        <v>0.04070595256760523</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.05497558930700319</v>
+      </c>
+      <c r="F46" t="n">
         <v>0.03002672334210166</v>
       </c>
-      <c r="E46" t="n">
+      <c r="G46" t="n">
         <v>-0.03183047021359953</v>
       </c>
-      <c r="F46" t="n">
+      <c r="H46" t="n">
         <v>-0.06201511497194401</v>
       </c>
-      <c r="G46" t="n">
+      <c r="I46" t="n">
         <v>0.038</v>
       </c>
-      <c r="H46" t="n">
+      <c r="J46" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I46" t="n">
+      <c r="K46" t="n">
         <v>0.1617002664602709</v>
       </c>
-      <c r="J46" t="n">
+      <c r="L46" t="n">
         <v>0.1045171306043</v>
       </c>
-      <c r="K46" t="n">
+      <c r="M46" t="n">
+        <v>35.86688263310138</v>
+      </c>
+      <c r="N46" t="n">
+        <v>34.41543826978847</v>
+      </c>
+      <c r="O46" t="n">
         <v>29.61332618959294</v>
       </c>
     </row>
@@ -2047,30 +2605,42 @@
         <v>44834</v>
       </c>
       <c r="C47" t="n">
-        <v>0.05874355773847133</v>
+        <v>-0.01044164876172315</v>
       </c>
       <c r="D47" t="n">
+        <v>0.03579798985912208</v>
+      </c>
+      <c r="E47" t="n">
+        <v>-0.04003849998357267</v>
+      </c>
+      <c r="F47" t="n">
         <v>0.05497558930700319</v>
       </c>
-      <c r="E47" t="n">
+      <c r="G47" t="n">
         <v>0.03240148834057766</v>
       </c>
-      <c r="F47" t="n">
+      <c r="H47" t="n">
         <v>-0.03183047021359953</v>
       </c>
-      <c r="G47" t="n">
+      <c r="I47" t="n">
         <v>0.039</v>
       </c>
-      <c r="H47" t="n">
+      <c r="J47" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I47" t="n">
+      <c r="K47" t="n">
         <v>0.01280741112165629</v>
       </c>
-      <c r="J47" t="n">
+      <c r="L47" t="n">
         <v>0.1617002664602709</v>
       </c>
-      <c r="K47" t="n">
+      <c r="M47" t="n">
+        <v>31.48670245276412</v>
+      </c>
+      <c r="N47" t="n">
+        <v>35.86688263310138</v>
+      </c>
+      <c r="O47" t="n">
         <v>34.41543826978847</v>
       </c>
     </row>
@@ -2082,30 +2652,42 @@
         <v>44865</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.03028176636188742</v>
+        <v>0.04332711530793776</v>
       </c>
       <c r="D48" t="n">
+        <v>-0.01044164876172315</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.008833967484206173</v>
+      </c>
+      <c r="F48" t="n">
         <v>-0.04003849998357267</v>
       </c>
-      <c r="E48" t="n">
+      <c r="G48" t="n">
         <v>0.00773697117163441</v>
       </c>
-      <c r="F48" t="n">
+      <c r="H48" t="n">
         <v>0.03240148834057766</v>
       </c>
-      <c r="G48" t="n">
+      <c r="I48" t="n">
         <v>0.039</v>
       </c>
-      <c r="H48" t="n">
+      <c r="J48" t="n">
         <v>0</v>
       </c>
-      <c r="I48" t="n">
+      <c r="K48" t="n">
         <v>-0.0663439586757133</v>
       </c>
-      <c r="J48" t="n">
+      <c r="L48" t="n">
         <v>0.01280741112165629</v>
       </c>
-      <c r="K48" t="n">
+      <c r="M48" t="n">
+        <v>35.53965895863496</v>
+      </c>
+      <c r="N48" t="n">
+        <v>31.48670245276412</v>
+      </c>
+      <c r="O48" t="n">
         <v>35.86688263310138</v>
       </c>
     </row>
@@ -2117,30 +2699,42 @@
         <v>44895</v>
       </c>
       <c r="C49" t="n">
-        <v>0.03751317113327821</v>
+        <v>-0.03355850069909661</v>
       </c>
       <c r="D49" t="n">
+        <v>0.04332711530793776</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.009460598990947977</v>
+      </c>
+      <c r="F49" t="n">
         <v>0.008833967484206173</v>
       </c>
-      <c r="E49" t="n">
+      <c r="G49" t="n">
         <v>0.005723356955285919</v>
       </c>
-      <c r="F49" t="n">
+      <c r="H49" t="n">
         <v>0.00773697117163441</v>
       </c>
-      <c r="G49" t="n">
+      <c r="I49" t="n">
         <v>0.037</v>
       </c>
-      <c r="H49" t="n">
+      <c r="J49" t="n">
         <v>-0.002000000000000002</v>
       </c>
-      <c r="I49" t="n">
+      <c r="K49" t="n">
         <v>0.08411725958830329</v>
       </c>
-      <c r="J49" t="n">
+      <c r="L49" t="n">
         <v>-0.0663439586757133</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
+        <v>36.18815100928686</v>
+      </c>
+      <c r="N49" t="n">
+        <v>35.53965895863496</v>
+      </c>
+      <c r="O49" t="n">
         <v>31.48670245276412</v>
       </c>
     </row>
@@ -2152,30 +2746,42 @@
         <v>44926</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.04035445792195602</v>
+        <v>0.07423687237173437</v>
       </c>
       <c r="D50" t="n">
+        <v>-0.03355850069909661</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.1460909848204688</v>
+      </c>
+      <c r="F50" t="n">
         <v>0.009460598990947977</v>
       </c>
-      <c r="E50" t="n">
+      <c r="G50" t="n">
         <v>0.3920597896508722</v>
       </c>
-      <c r="F50" t="n">
+      <c r="H50" t="n">
         <v>0.005723356955285919</v>
       </c>
-      <c r="G50" t="n">
+      <c r="I50" t="n">
         <v>0.037</v>
       </c>
-      <c r="H50" t="n">
+      <c r="J50" t="n">
         <v>0</v>
       </c>
-      <c r="I50" t="n">
+      <c r="K50" t="n">
         <v>0.1917443220988235</v>
       </c>
-      <c r="J50" t="n">
+      <c r="L50" t="n">
         <v>0.08411725958830329</v>
       </c>
-      <c r="K50" t="n">
+      <c r="M50" t="n">
+        <v>37.38990117016424</v>
+      </c>
+      <c r="N50" t="n">
+        <v>36.18815100928686</v>
+      </c>
+      <c r="O50" t="n">
         <v>35.53965895863496</v>
       </c>
     </row>
@@ -2187,30 +2793,42 @@
         <v>44957</v>
       </c>
       <c r="C51" t="n">
-        <v>0.1564478022623059</v>
+        <v>-0.2711844412369511</v>
       </c>
       <c r="D51" t="n">
+        <v>0.07423687237173437</v>
+      </c>
+      <c r="E51" t="n">
+        <v>-0.1478599195476036</v>
+      </c>
+      <c r="F51" t="n">
         <v>0.1460909848204688</v>
       </c>
-      <c r="E51" t="n">
+      <c r="G51" t="n">
         <v>-0.2908956634774742</v>
       </c>
-      <c r="F51" t="n">
+      <c r="H51" t="n">
         <v>0.3920597896508722</v>
       </c>
-      <c r="G51" t="n">
+      <c r="I51" t="n">
         <v>0.036</v>
       </c>
-      <c r="H51" t="n">
+      <c r="J51" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I51" t="n">
+      <c r="K51" t="n">
         <v>-0.3368545128771974</v>
       </c>
-      <c r="J51" t="n">
+      <c r="L51" t="n">
         <v>0.1917443220988235</v>
       </c>
-      <c r="K51" t="n">
+      <c r="M51" t="n">
+        <v>36.79678996154339</v>
+      </c>
+      <c r="N51" t="n">
+        <v>37.38990117016424</v>
+      </c>
+      <c r="O51" t="n">
         <v>36.18815100928686</v>
       </c>
     </row>
@@ -2222,30 +2840,42 @@
         <v>44985</v>
       </c>
       <c r="C52" t="n">
-        <v>-0.6215216295367832</v>
+        <v>0.1365122612217451</v>
       </c>
       <c r="D52" t="n">
+        <v>-0.2711844412369511</v>
+      </c>
+      <c r="E52" t="n">
+        <v>-0.02074610964740808</v>
+      </c>
+      <c r="F52" t="n">
         <v>-0.1478599195476036</v>
       </c>
-      <c r="E52" t="n">
+      <c r="G52" t="n">
         <v>0.02427977682678661</v>
       </c>
-      <c r="F52" t="n">
+      <c r="H52" t="n">
         <v>-0.2908956634774742</v>
       </c>
-      <c r="G52" t="n">
+      <c r="I52" t="n">
         <v>0.035</v>
       </c>
-      <c r="H52" t="n">
+      <c r="J52" t="n">
         <v>-0.0009999999999999939</v>
       </c>
-      <c r="I52" t="n">
+      <c r="K52" t="n">
         <v>0.1465965671210288</v>
       </c>
-      <c r="J52" t="n">
+      <c r="L52" t="n">
         <v>-0.3368545128771974</v>
       </c>
-      <c r="K52" t="n">
+      <c r="M52" t="n">
+        <v>40.77530607249603</v>
+      </c>
+      <c r="N52" t="n">
+        <v>36.79678996154339</v>
+      </c>
+      <c r="O52" t="n">
         <v>37.38990117016424</v>
       </c>
     </row>
@@ -2257,30 +2887,42 @@
         <v>45016</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4271324313579455</v>
+        <v>0.1060705921640062</v>
       </c>
       <c r="D53" t="n">
+        <v>0.1365122612217451</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.1005349070171786</v>
+      </c>
+      <c r="F53" t="n">
         <v>-0.02074610964740808</v>
       </c>
-      <c r="E53" t="n">
+      <c r="G53" t="n">
         <v>0.09182162968167207</v>
       </c>
-      <c r="F53" t="n">
+      <c r="H53" t="n">
         <v>0.02427977682678661</v>
       </c>
-      <c r="G53" t="n">
+      <c r="I53" t="n">
         <v>0.035</v>
       </c>
-      <c r="H53" t="n">
+      <c r="J53" t="n">
         <v>0</v>
       </c>
-      <c r="I53" t="n">
+      <c r="K53" t="n">
         <v>0.2830303562323382</v>
       </c>
-      <c r="J53" t="n">
+      <c r="L53" t="n">
         <v>0.1465965671210288</v>
       </c>
-      <c r="K53" t="n">
+      <c r="M53" t="n">
+        <v>43.6391094808851</v>
+      </c>
+      <c r="N53" t="n">
+        <v>40.77530607249603</v>
+      </c>
+      <c r="O53" t="n">
         <v>36.79678996154339</v>
       </c>
     </row>
@@ -2292,30 +2934,42 @@
         <v>45046</v>
       </c>
       <c r="C54" t="n">
-        <v>0.1783130527343908</v>
+        <v>-0.1269034089928103</v>
       </c>
       <c r="D54" t="n">
+        <v>0.1060705921640062</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.004522162192526658</v>
+      </c>
+      <c r="F54" t="n">
         <v>0.1005349070171786</v>
       </c>
-      <c r="E54" t="n">
+      <c r="G54" t="n">
         <v>-0.005601128586019244</v>
       </c>
-      <c r="F54" t="n">
+      <c r="H54" t="n">
         <v>0.09182162968167207</v>
       </c>
-      <c r="G54" t="n">
+      <c r="I54" t="n">
         <v>0.033</v>
       </c>
-      <c r="H54" t="n">
+      <c r="J54" t="n">
         <v>-0.002000000000000002</v>
       </c>
-      <c r="I54" t="n">
+      <c r="K54" t="n">
         <v>-0.0254915718751304</v>
       </c>
-      <c r="J54" t="n">
+      <c r="L54" t="n">
         <v>0.2830303562323382</v>
       </c>
-      <c r="K54" t="n">
+      <c r="M54" t="n">
+        <v>40.40000000000001</v>
+      </c>
+      <c r="N54" t="n">
+        <v>43.6391094808851</v>
+      </c>
+      <c r="O54" t="n">
         <v>40.77530607249603</v>
       </c>
     </row>
@@ -2327,30 +2981,42 @@
         <v>45077</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.2431353512400235</v>
+        <v>0.01011448896633826</v>
       </c>
       <c r="D55" t="n">
+        <v>-0.1269034089928103</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.03135046379465312</v>
+      </c>
+      <c r="F55" t="n">
         <v>0.004522162192526658</v>
       </c>
-      <c r="E55" t="n">
+      <c r="G55" t="n">
         <v>0.01996881965216857</v>
       </c>
-      <c r="F55" t="n">
+      <c r="H55" t="n">
         <v>-0.005601128586019244</v>
       </c>
-      <c r="G55" t="n">
+      <c r="I55" t="n">
         <v>0.032</v>
       </c>
-      <c r="H55" t="n">
+      <c r="J55" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I55" t="n">
+      <c r="K55" t="n">
         <v>0.06686587289573698</v>
       </c>
-      <c r="J55" t="n">
+      <c r="L55" t="n">
         <v>-0.0254915718751304</v>
       </c>
-      <c r="K55" t="n">
+      <c r="M55" t="n">
+        <v>41.95641493526392</v>
+      </c>
+      <c r="N55" t="n">
+        <v>40.40000000000001</v>
+      </c>
+      <c r="O55" t="n">
         <v>43.6391094808851</v>
       </c>
     </row>
@@ -2362,30 +3028,42 @@
         <v>45107</v>
       </c>
       <c r="C56" t="n">
-        <v>0.02290620799203023</v>
+        <v>0.01534874595292579</v>
       </c>
       <c r="D56" t="n">
+        <v>0.01011448896633826</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.03925814452257259</v>
+      </c>
+      <c r="F56" t="n">
         <v>0.03135046379465312</v>
       </c>
-      <c r="E56" t="n">
+      <c r="G56" t="n">
         <v>0.04763984080989236</v>
       </c>
-      <c r="F56" t="n">
+      <c r="H56" t="n">
         <v>0.01996881965216857</v>
       </c>
-      <c r="G56" t="n">
+      <c r="I56" t="n">
         <v>0.031</v>
       </c>
-      <c r="H56" t="n">
+      <c r="J56" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I56" t="n">
+      <c r="K56" t="n">
         <v>0.02790873293129681</v>
       </c>
-      <c r="J56" t="n">
+      <c r="L56" t="n">
         <v>0.06686587289573698</v>
       </c>
-      <c r="K56" t="n">
+      <c r="M56" t="n">
+        <v>44.87215874030626</v>
+      </c>
+      <c r="N56" t="n">
+        <v>41.95641493526392</v>
+      </c>
+      <c r="O56" t="n">
         <v>40.40000000000001</v>
       </c>
     </row>
@@ -2397,30 +3075,42 @@
         <v>45138</v>
       </c>
       <c r="C57" t="n">
-        <v>0.03461362554943809</v>
+        <v>0.03390120904559013</v>
       </c>
       <c r="D57" t="n">
+        <v>0.01534874595292579</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.06532220081436857</v>
+      </c>
+      <c r="F57" t="n">
         <v>0.03925814452257259</v>
       </c>
-      <c r="E57" t="n">
+      <c r="G57" t="n">
         <v>-0.07352256835406723</v>
       </c>
-      <c r="F57" t="n">
+      <c r="H57" t="n">
         <v>0.04763984080989236</v>
       </c>
-      <c r="G57" t="n">
+      <c r="I57" t="n">
         <v>0.03</v>
       </c>
-      <c r="H57" t="n">
+      <c r="J57" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I57" t="n">
+      <c r="K57" t="n">
         <v>0.04841926127458018</v>
       </c>
-      <c r="J57" t="n">
+      <c r="L57" t="n">
         <v>0.02790873293129681</v>
       </c>
-      <c r="K57" t="n">
+      <c r="M57" t="n">
+        <v>42.71891946151892</v>
+      </c>
+      <c r="N57" t="n">
+        <v>44.87215874030626</v>
+      </c>
+      <c r="O57" t="n">
         <v>41.95641493526392</v>
       </c>
     </row>
@@ -2432,30 +3122,42 @@
         <v>45169</v>
       </c>
       <c r="C58" t="n">
-        <v>-0.008864259348781682</v>
+        <v>0.01023790590378715</v>
       </c>
       <c r="D58" t="n">
+        <v>0.03390120904559013</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.06535247803628597</v>
+      </c>
+      <c r="F58" t="n">
         <v>0.06532220081436857</v>
       </c>
-      <c r="E58" t="n">
+      <c r="G58" t="n">
         <v>-0.03043848721360887</v>
       </c>
-      <c r="F58" t="n">
+      <c r="H58" t="n">
         <v>-0.07352256835406723</v>
       </c>
-      <c r="G58" t="n">
+      <c r="I58" t="n">
         <v>0.03</v>
       </c>
-      <c r="H58" t="n">
+      <c r="J58" t="n">
         <v>0</v>
       </c>
-      <c r="I58" t="n">
+      <c r="K58" t="n">
         <v>0.1488307190997415</v>
       </c>
-      <c r="J58" t="n">
+      <c r="L58" t="n">
         <v>0.04841926127458018</v>
       </c>
-      <c r="K58" t="n">
+      <c r="M58" t="n">
+        <v>40.03403049175887</v>
+      </c>
+      <c r="N58" t="n">
+        <v>42.71891946151892</v>
+      </c>
+      <c r="O58" t="n">
         <v>44.87215874030626</v>
       </c>
     </row>
@@ -2467,30 +3169,42 @@
         <v>45199</v>
       </c>
       <c r="C59" t="n">
-        <v>0.02694745894898453</v>
+        <v>-0.01379314719192859</v>
       </c>
       <c r="D59" t="n">
+        <v>0.01023790590378715</v>
+      </c>
+      <c r="E59" t="n">
+        <v>-0.02941065188457048</v>
+      </c>
+      <c r="F59" t="n">
         <v>0.06535247803628597</v>
       </c>
-      <c r="E59" t="n">
+      <c r="G59" t="n">
         <v>0.012547709307972</v>
       </c>
-      <c r="F59" t="n">
+      <c r="H59" t="n">
         <v>-0.03043848721360887</v>
       </c>
-      <c r="G59" t="n">
+      <c r="I59" t="n">
         <v>0.03</v>
       </c>
-      <c r="H59" t="n">
+      <c r="J59" t="n">
         <v>0</v>
       </c>
-      <c r="I59" t="n">
+      <c r="K59" t="n">
         <v>-0.02847196043246825</v>
       </c>
-      <c r="J59" t="n">
+      <c r="L59" t="n">
         <v>0.1488307190997415</v>
       </c>
-      <c r="K59" t="n">
+      <c r="M59" t="n">
+        <v>43.14882114202203</v>
+      </c>
+      <c r="N59" t="n">
+        <v>40.03403049175887</v>
+      </c>
+      <c r="O59" t="n">
         <v>42.71891946151892</v>
       </c>
     </row>
@@ -2502,30 +3216,42 @@
         <v>45230</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.02472343074875858</v>
+        <v>0.07557310785575444</v>
       </c>
       <c r="D60" t="n">
+        <v>-0.01379314719192859</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.02202866126110048</v>
+      </c>
+      <c r="F60" t="n">
         <v>-0.02941065188457048</v>
       </c>
-      <c r="E60" t="n">
+      <c r="G60" t="n">
         <v>0.03243359297772663</v>
       </c>
-      <c r="F60" t="n">
+      <c r="H60" t="n">
         <v>0.012547709307972</v>
       </c>
-      <c r="G60" t="n">
+      <c r="I60" t="n">
         <v>0.029</v>
       </c>
-      <c r="H60" t="n">
+      <c r="J60" t="n">
         <v>-0.0009999999999999974</v>
       </c>
-      <c r="I60" t="n">
+      <c r="K60" t="n">
         <v>-0.05502195639917384</v>
       </c>
-      <c r="J60" t="n">
+      <c r="L60" t="n">
         <v>-0.02847196043246825</v>
       </c>
-      <c r="K60" t="n">
+      <c r="M60" t="n">
+        <v>42.29132093870246</v>
+      </c>
+      <c r="N60" t="n">
+        <v>43.14882114202203</v>
+      </c>
+      <c r="O60" t="n">
         <v>40.03403049175887</v>
       </c>
     </row>
@@ -2537,30 +3263,42 @@
         <v>45260</v>
       </c>
       <c r="C61" t="n">
-        <v>0.05942864666920916</v>
+        <v>-0.05847851040544216</v>
       </c>
       <c r="D61" t="n">
+        <v>0.07557310785575444</v>
+      </c>
+      <c r="E61" t="n">
+        <v>-0.04018617212850384</v>
+      </c>
+      <c r="F61" t="n">
         <v>0.02202866126110048</v>
       </c>
-      <c r="E61" t="n">
+      <c r="G61" t="n">
         <v>-0.01696612541866149</v>
       </c>
-      <c r="F61" t="n">
+      <c r="H61" t="n">
         <v>0.03243359297772663</v>
       </c>
-      <c r="G61" t="n">
+      <c r="I61" t="n">
         <v>0.029</v>
       </c>
-      <c r="H61" t="n">
+      <c r="J61" t="n">
         <v>0</v>
       </c>
-      <c r="I61" t="n">
+      <c r="K61" t="n">
         <v>-0.04390492877213281</v>
       </c>
-      <c r="J61" t="n">
+      <c r="L61" t="n">
         <v>-0.05502195639917384</v>
       </c>
-      <c r="K61" t="n">
+      <c r="M61" t="n">
+        <v>38.98105162104949</v>
+      </c>
+      <c r="N61" t="n">
+        <v>42.29132093870246</v>
+      </c>
+      <c r="O61" t="n">
         <v>43.14882114202203</v>
       </c>
     </row>
@@ -2572,30 +3310,42 @@
         <v>45291</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.06271363125320087</v>
+        <v>0.09086198292519576</v>
       </c>
       <c r="D62" t="n">
+        <v>-0.05847851040544216</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.1462943385567161</v>
+      </c>
+      <c r="F62" t="n">
         <v>-0.04018617212850384</v>
       </c>
-      <c r="E62" t="n">
+      <c r="G62" t="n">
         <v>0.4044484786426001</v>
       </c>
-      <c r="F62" t="n">
+      <c r="H62" t="n">
         <v>-0.01696612541866149</v>
       </c>
-      <c r="G62" t="n">
+      <c r="I62" t="n">
         <v>0.03</v>
       </c>
-      <c r="H62" t="n">
+      <c r="J62" t="n">
         <v>0.0009999999999999974</v>
       </c>
-      <c r="I62" t="n">
+      <c r="K62" t="n">
         <v>0.03585249968970494</v>
       </c>
-      <c r="J62" t="n">
+      <c r="L62" t="n">
         <v>-0.04390492877213281</v>
       </c>
-      <c r="K62" t="n">
+      <c r="M62" t="n">
+        <v>41.55227666692885</v>
+      </c>
+      <c r="N62" t="n">
+        <v>38.98105162104949</v>
+      </c>
+      <c r="O62" t="n">
         <v>42.29132093870246</v>
       </c>
     </row>
@@ -2607,30 +3357,42 @@
         <v>45322</v>
       </c>
       <c r="C63" t="n">
-        <v>0.1675951895088274</v>
+        <v>-0.2729902954392507</v>
       </c>
       <c r="D63" t="n">
+        <v>0.09086198292519576</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-0.1676363642817396</v>
+      </c>
+      <c r="F63" t="n">
         <v>0.1462943385567161</v>
       </c>
-      <c r="E63" t="n">
+      <c r="G63" t="n">
         <v>-0.2833963319774938</v>
       </c>
-      <c r="F63" t="n">
+      <c r="H63" t="n">
         <v>0.4044484786426001</v>
       </c>
-      <c r="G63" t="n">
+      <c r="I63" t="n">
         <v>0.029</v>
       </c>
-      <c r="H63" t="n">
+      <c r="J63" t="n">
         <v>-0.0009999999999999974</v>
       </c>
-      <c r="I63" t="n">
+      <c r="K63" t="n">
         <v>-0.2889698574863314</v>
       </c>
-      <c r="J63" t="n">
+      <c r="L63" t="n">
         <v>0.03585249968970494</v>
       </c>
-      <c r="K63" t="n">
+      <c r="M63" t="n">
+        <v>42.26318235577299</v>
+      </c>
+      <c r="N63" t="n">
+        <v>41.55227666692885</v>
+      </c>
+      <c r="O63" t="n">
         <v>38.98105162104949</v>
       </c>
     </row>
@@ -2642,30 +3404,42 @@
         <v>45351</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.6122343987464899</v>
+        <v>0.155262227665955</v>
       </c>
       <c r="D64" t="n">
+        <v>-0.2729902954392507</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.02001837599371803</v>
+      </c>
+      <c r="F64" t="n">
         <v>-0.1676363642817396</v>
       </c>
-      <c r="E64" t="n">
+      <c r="G64" t="n">
         <v>0.0382261987994128</v>
       </c>
-      <c r="F64" t="n">
+      <c r="H64" t="n">
         <v>-0.2833963319774938</v>
       </c>
-      <c r="G64" t="n">
+      <c r="I64" t="n">
         <v>0.028</v>
       </c>
-      <c r="H64" t="n">
+      <c r="J64" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I64" t="n">
+      <c r="K64" t="n">
         <v>0.1392328594586401</v>
       </c>
-      <c r="J64" t="n">
+      <c r="L64" t="n">
         <v>-0.2889698574863314</v>
       </c>
-      <c r="K64" t="n">
+      <c r="M64" t="n">
+        <v>42.81374221963993</v>
+      </c>
+      <c r="N64" t="n">
+        <v>42.26318235577299</v>
+      </c>
+      <c r="O64" t="n">
         <v>41.55227666692885</v>
       </c>
     </row>
@@ -2677,30 +3451,42 @@
         <v>45382</v>
       </c>
       <c r="C65" t="n">
-        <v>0.4788476629169152</v>
+        <v>0.04877210466284043</v>
       </c>
       <c r="D65" t="n">
+        <v>0.155262227665955</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.1016453563309765</v>
+      </c>
+      <c r="F65" t="n">
         <v>0.02001837599371803</v>
       </c>
-      <c r="E65" t="n">
+      <c r="G65" t="n">
         <v>0.1143301629560669</v>
       </c>
-      <c r="F65" t="n">
+      <c r="H65" t="n">
         <v>0.0382261987994128</v>
       </c>
-      <c r="G65" t="n">
+      <c r="I65" t="n">
         <v>0.027</v>
       </c>
-      <c r="H65" t="n">
+      <c r="J65" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I65" t="n">
+      <c r="K65" t="n">
         <v>0.2401137115118062</v>
       </c>
-      <c r="J65" t="n">
+      <c r="L65" t="n">
         <v>0.1392328594586401</v>
       </c>
-      <c r="K65" t="n">
+      <c r="M65" t="n">
+        <v>44.36566608603261</v>
+      </c>
+      <c r="N65" t="n">
+        <v>42.81374221963993</v>
+      </c>
+      <c r="O65" t="n">
         <v>42.26318235577299</v>
       </c>
     </row>
@@ -2712,30 +3498,42 @@
         <v>45412</v>
       </c>
       <c r="C66" t="n">
-        <v>0.04747486384315448</v>
+        <v>-0.1071185731222313</v>
       </c>
       <c r="D66" t="n">
+        <v>0.04877210466284043</v>
+      </c>
+      <c r="E66" t="n">
+        <v>-0.02990382170520123</v>
+      </c>
+      <c r="F66" t="n">
         <v>0.1016453563309765</v>
       </c>
-      <c r="E66" t="n">
+      <c r="G66" t="n">
         <v>-0.04880657120143539</v>
       </c>
-      <c r="F66" t="n">
+      <c r="H66" t="n">
         <v>0.1143301629560669</v>
       </c>
-      <c r="G66" t="n">
+      <c r="I66" t="n">
         <v>0.026</v>
       </c>
-      <c r="H66" t="n">
+      <c r="J66" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I66" t="n">
+      <c r="K66" t="n">
         <v>0.01087447323997148</v>
       </c>
-      <c r="J66" t="n">
+      <c r="L66" t="n">
         <v>0.2401137115118062</v>
       </c>
-      <c r="K66" t="n">
+      <c r="M66" t="n">
+        <v>43.1772628446213</v>
+      </c>
+      <c r="N66" t="n">
+        <v>44.36566608603261</v>
+      </c>
+      <c r="O66" t="n">
         <v>42.81374221963993</v>
       </c>
     </row>
@@ -2747,30 +3545,42 @@
         <v>45443</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1661090563423909</v>
+        <v>0.04494628544430812</v>
       </c>
       <c r="D67" t="n">
+        <v>-0.1071185731222313</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.01754561204088478</v>
+      </c>
+      <c r="F67" t="n">
         <v>-0.02990382170520123</v>
       </c>
-      <c r="E67" t="n">
+      <c r="G67" t="n">
         <v>0.02234818527693871</v>
       </c>
-      <c r="F67" t="n">
+      <c r="H67" t="n">
         <v>-0.04880657120143539</v>
       </c>
-      <c r="G67" t="n">
+      <c r="I67" t="n">
         <v>0.026</v>
       </c>
-      <c r="H67" t="n">
+      <c r="J67" t="n">
         <v>0</v>
       </c>
-      <c r="I67" t="n">
+      <c r="K67" t="n">
         <v>0.1069587865638131</v>
       </c>
-      <c r="J67" t="n">
+      <c r="L67" t="n">
         <v>0.01087447323997148</v>
       </c>
-      <c r="K67" t="n">
+      <c r="M67" t="n">
+        <v>44.90708177111237</v>
+      </c>
+      <c r="N67" t="n">
+        <v>43.1772628446213</v>
+      </c>
+      <c r="O67" t="n">
         <v>44.36566608603261</v>
       </c>
     </row>
@@ -2782,30 +3592,42 @@
         <v>45473</v>
       </c>
       <c r="C68" t="n">
-        <v>0.04411114224258187</v>
+        <v>-0.024392461993336</v>
       </c>
       <c r="D68" t="n">
+        <v>0.04494628544430812</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.02348331947019933</v>
+      </c>
+      <c r="F68" t="n">
         <v>0.01754561204088478</v>
       </c>
-      <c r="E68" t="n">
+      <c r="G68" t="n">
         <v>0.02539938135514119</v>
       </c>
-      <c r="F68" t="n">
+      <c r="H68" t="n">
         <v>0.02234818527693871</v>
       </c>
-      <c r="G68" t="n">
+      <c r="I68" t="n">
         <v>0.024</v>
       </c>
-      <c r="H68" t="n">
+      <c r="J68" t="n">
         <v>-0.001999999999999998</v>
       </c>
-      <c r="I68" t="n">
+      <c r="K68" t="n">
         <v>0.1046726503778119</v>
       </c>
-      <c r="J68" t="n">
+      <c r="L68" t="n">
         <v>0.1069587865638131</v>
       </c>
-      <c r="K68" t="n">
+      <c r="M68" t="n">
+        <v>43.78506517257788</v>
+      </c>
+      <c r="N68" t="n">
+        <v>44.90708177111237</v>
+      </c>
+      <c r="O68" t="n">
         <v>43.1772628446213</v>
       </c>
     </row>
@@ -2817,30 +3639,42 @@
         <v>45504</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.03202163199004163</v>
+        <v>0.05840071030214067</v>
       </c>
       <c r="D69" t="n">
+        <v>-0.024392461993336</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.05139354047914257</v>
+      </c>
+      <c r="F69" t="n">
         <v>0.02348331947019933</v>
       </c>
-      <c r="E69" t="n">
+      <c r="G69" t="n">
         <v>-0.05705613918209418</v>
       </c>
-      <c r="F69" t="n">
+      <c r="H69" t="n">
         <v>0.02539938135514119</v>
       </c>
-      <c r="G69" t="n">
+      <c r="I69" t="n">
         <v>0.024</v>
       </c>
-      <c r="H69" t="n">
+      <c r="J69" t="n">
         <v>0</v>
       </c>
-      <c r="I69" t="n">
+      <c r="K69" t="n">
         <v>-0.2220436605986137</v>
       </c>
-      <c r="J69" t="n">
+      <c r="L69" t="n">
         <v>0.1046726503778119</v>
       </c>
-      <c r="K69" t="n">
+      <c r="M69" t="n">
+        <v>44.67990317308502</v>
+      </c>
+      <c r="N69" t="n">
+        <v>43.78506517257788</v>
+      </c>
+      <c r="O69" t="n">
         <v>44.90708177111237</v>
       </c>
     </row>
@@ -2852,30 +3686,42 @@
         <v>45535</v>
       </c>
       <c r="C70" t="n">
-        <v>0.04658200706639726</v>
+        <v>-0.01668611174915879</v>
       </c>
       <c r="D70" t="n">
+        <v>0.05840071030214067</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.04120823087244974</v>
+      </c>
+      <c r="F70" t="n">
         <v>0.05139354047914257</v>
       </c>
-      <c r="E70" t="n">
+      <c r="G70" t="n">
         <v>-0.03485312095735127</v>
       </c>
-      <c r="F70" t="n">
+      <c r="H70" t="n">
         <v>-0.05705613918209418</v>
       </c>
-      <c r="G70" t="n">
+      <c r="I70" t="n">
         <v>0.024</v>
       </c>
-      <c r="H70" t="n">
+      <c r="J70" t="n">
         <v>0</v>
       </c>
-      <c r="I70" t="n">
+      <c r="K70" t="n">
         <v>-0.01928437794136018</v>
       </c>
-      <c r="J70" t="n">
+      <c r="L70" t="n">
         <v>-0.2220436605986137</v>
       </c>
-      <c r="K70" t="n">
+      <c r="M70" t="n">
+        <v>43.84854764618955</v>
+      </c>
+      <c r="N70" t="n">
+        <v>44.67990317308502</v>
+      </c>
+      <c r="O70" t="n">
         <v>43.78506517257788</v>
       </c>
     </row>
@@ -2887,30 +3733,42 @@
         <v>45565</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.02600512923391139</v>
+        <v>0.00126417015612712</v>
       </c>
       <c r="D71" t="n">
+        <v>-0.01668611174915879</v>
+      </c>
+      <c r="E71" t="n">
+        <v>-0.01305037056901925</v>
+      </c>
+      <c r="F71" t="n">
         <v>0.04120823087244974</v>
       </c>
-      <c r="E71" t="n">
+      <c r="G71" t="n">
         <v>0.02071539497371666</v>
       </c>
-      <c r="F71" t="n">
+      <c r="H71" t="n">
         <v>-0.03485312095735127</v>
       </c>
-      <c r="G71" t="n">
+      <c r="I71" t="n">
         <v>0.024</v>
       </c>
-      <c r="H71" t="n">
+      <c r="J71" t="n">
         <v>0</v>
       </c>
-      <c r="I71" t="n">
+      <c r="K71" t="n">
         <v>-0.06715971126300113</v>
       </c>
-      <c r="J71" t="n">
+      <c r="L71" t="n">
         <v>-0.01928437794136018</v>
       </c>
-      <c r="K71" t="n">
+      <c r="M71" t="n">
+        <v>40.80883798060322</v>
+      </c>
+      <c r="N71" t="n">
+        <v>43.84854764618955</v>
+      </c>
+      <c r="O71" t="n">
         <v>44.67990317308502</v>
       </c>
     </row>
@@ -2922,30 +3780,42 @@
         <v>45596</v>
       </c>
       <c r="C72" t="n">
-        <v>0.008130873841376981</v>
+        <v>0.09434134542023176</v>
       </c>
       <c r="D72" t="n">
+        <v>0.00126417015612712</v>
+      </c>
+      <c r="E72" t="n">
+        <v>-0.007618355518545505</v>
+      </c>
+      <c r="F72" t="n">
         <v>-0.01305037056901925</v>
       </c>
-      <c r="E72" t="n">
+      <c r="G72" t="n">
         <v>0.01913416088693931</v>
       </c>
-      <c r="F72" t="n">
+      <c r="H72" t="n">
         <v>0.02071539497371666</v>
       </c>
-      <c r="G72" t="n">
+      <c r="I72" t="n">
         <v>0.023</v>
       </c>
-      <c r="H72" t="n">
+      <c r="J72" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I72" t="n">
+      <c r="K72" t="n">
         <v>-0.07252828605971218</v>
       </c>
-      <c r="J72" t="n">
+      <c r="L72" t="n">
         <v>-0.06715971126300113</v>
       </c>
-      <c r="K72" t="n">
+      <c r="M72" t="n">
+        <v>41.81478969714814</v>
+      </c>
+      <c r="N72" t="n">
+        <v>40.80883798060322</v>
+      </c>
+      <c r="O72" t="n">
         <v>43.84854764618955</v>
       </c>
     </row>
@@ -2957,30 +3827,42 @@
         <v>45626</v>
       </c>
       <c r="C73" t="n">
-        <v>0.1073190676198935</v>
+        <v>-0.07994278310163749</v>
       </c>
       <c r="D73" t="n">
+        <v>0.09434134542023176</v>
+      </c>
+      <c r="E73" t="n">
+        <v>-0.01968677834015709</v>
+      </c>
+      <c r="F73" t="n">
         <v>-0.007618355518545505</v>
       </c>
-      <c r="E73" t="n">
+      <c r="G73" t="n">
         <v>-0.01618219785996977</v>
       </c>
-      <c r="F73" t="n">
+      <c r="H73" t="n">
         <v>0.01913416088693931</v>
       </c>
-      <c r="G73" t="n">
+      <c r="I73" t="n">
         <v>0.023</v>
       </c>
-      <c r="H73" t="n">
+      <c r="J73" t="n">
         <v>0</v>
       </c>
-      <c r="I73" t="n">
+      <c r="K73" t="n">
         <v>-0.1310157005985541</v>
       </c>
-      <c r="J73" t="n">
+      <c r="L73" t="n">
         <v>-0.07252828605971218</v>
       </c>
-      <c r="K73" t="n">
+      <c r="M73" t="n">
+        <v>41.50170160472339</v>
+      </c>
+      <c r="N73" t="n">
+        <v>41.81478969714814</v>
+      </c>
+      <c r="O73" t="n">
         <v>40.80883798060322</v>
       </c>
     </row>
@@ -2992,30 +3874,42 @@
         <v>45657</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.1326336334582725</v>
+        <v>0.1207962141607717</v>
       </c>
       <c r="D74" t="n">
+        <v>-0.07994278310163749</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.1480122167754947</v>
+      </c>
+      <c r="F74" t="n">
         <v>-0.01968677834015709</v>
       </c>
-      <c r="E74" t="n">
+      <c r="G74" t="n">
         <v>0.469794193446013</v>
       </c>
-      <c r="F74" t="n">
+      <c r="H74" t="n">
         <v>-0.01618219785996977</v>
       </c>
-      <c r="G74" t="n">
+      <c r="I74" t="n">
         <v>0.023</v>
       </c>
-      <c r="H74" t="n">
+      <c r="J74" t="n">
         <v>0</v>
       </c>
-      <c r="I74" t="n">
+      <c r="K74" t="n">
         <v>0.2310314438024543</v>
       </c>
-      <c r="J74" t="n">
+      <c r="L74" t="n">
         <v>-0.1310157005985541</v>
       </c>
-      <c r="K74" t="n">
+      <c r="M74" t="n">
+        <v>40.27690958231305</v>
+      </c>
+      <c r="N74" t="n">
+        <v>41.50170160472339</v>
+      </c>
+      <c r="O74" t="n">
         <v>41.81478969714814</v>
       </c>
     </row>
@@ -3027,30 +3921,42 @@
         <v>45688</v>
       </c>
       <c r="C75" t="n">
-        <v>0.264260453139088</v>
+        <v>-0.3532009578915456</v>
       </c>
       <c r="D75" t="n">
+        <v>0.1207962141607717</v>
+      </c>
+      <c r="E75" t="n">
+        <v>-0.1755433348977434</v>
+      </c>
+      <c r="F75" t="n">
         <v>0.1480122167754947</v>
       </c>
-      <c r="E75" t="n">
+      <c r="G75" t="n">
         <v>-0.3168318340994584</v>
       </c>
-      <c r="F75" t="n">
+      <c r="H75" t="n">
         <v>0.469794193446013</v>
       </c>
-      <c r="G75" t="n">
+      <c r="I75" t="n">
         <v>0.024</v>
       </c>
-      <c r="H75" t="n">
+      <c r="J75" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I75" t="n">
+      <c r="K75" t="n">
         <v>-0.3441594918896017</v>
       </c>
-      <c r="J75" t="n">
+      <c r="L75" t="n">
         <v>0.2310314438024543</v>
       </c>
-      <c r="K75" t="n">
+      <c r="M75" t="n">
+        <v>39.1320251193151</v>
+      </c>
+      <c r="N75" t="n">
+        <v>40.27690958231305</v>
+      </c>
+      <c r="O75" t="n">
         <v>41.50170160472339</v>
       </c>
     </row>
@@ -3062,28 +3968,40 @@
         <v>45688</v>
       </c>
       <c r="C76" t="n">
-        <v>0.264260453139088</v>
+        <v>-0.3532009578915456</v>
       </c>
       <c r="D76" t="n">
+        <v>0.1207962141607717</v>
+      </c>
+      <c r="E76" t="n">
+        <v>-0.1755433348977434</v>
+      </c>
+      <c r="F76" t="n">
         <v>0.1480122167754947</v>
       </c>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="n">
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="n">
         <v>-0.3168318340994584</v>
       </c>
-      <c r="G76" t="n">
+      <c r="I76" t="n">
         <v>0.024</v>
       </c>
-      <c r="H76" t="n">
+      <c r="J76" t="n">
         <v>0.001000000000000001</v>
       </c>
-      <c r="I76" t="n">
+      <c r="K76" t="n">
         <v>-0.3441594918896017</v>
       </c>
-      <c r="J76" t="n">
+      <c r="L76" t="n">
         <v>-0.3441594918896017</v>
       </c>
-      <c r="K76" t="n">
+      <c r="M76" t="n">
+        <v>39.1320251193151</v>
+      </c>
+      <c r="N76" t="n">
+        <v>39.1320251193151</v>
+      </c>
+      <c r="O76" t="n">
         <v>40.27690958231305</v>
       </c>
     </row>
@@ -3095,28 +4013,40 @@
         <v>45716</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7933477312550334</v>
+        <v>0.1965123740843326</v>
       </c>
       <c r="D77" t="n">
+        <v>-0.3532009578915456</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.004243709152518038</v>
+      </c>
+      <c r="F77" t="n">
         <v>-0.1755433348977434</v>
       </c>
-      <c r="E77" t="n">
+      <c r="G77" t="n">
         <v>-0.0006214605893831715</v>
       </c>
-      <c r="F77" t="inlineStr"/>
-      <c r="G77" t="n">
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="n">
         <v>0.024</v>
       </c>
-      <c r="H77" t="n">
+      <c r="J77" t="n">
         <v>0</v>
       </c>
-      <c r="I77" t="n">
+      <c r="K77" t="n">
         <v>0.07461163879560084</v>
       </c>
-      <c r="J77" t="n">
+      <c r="L77" t="n">
         <v>-0.3441594918896017</v>
       </c>
-      <c r="K77" t="n">
+      <c r="M77" t="n">
+        <v>38.95216307515854</v>
+      </c>
+      <c r="N77" t="n">
+        <v>39.1320251193151</v>
+      </c>
+      <c r="O77" t="n">
         <v>39.1320251193151</v>
       </c>
     </row>
@@ -3128,30 +4058,42 @@
         <v>45747</v>
       </c>
       <c r="C78" t="n">
-        <v>0.5452164020188751</v>
+        <v>0.07292050156819641</v>
       </c>
       <c r="D78" t="n">
+        <v>0.1965123740843326</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.1112447881360432</v>
+      </c>
+      <c r="F78" t="n">
         <v>0.004243709152518038</v>
       </c>
-      <c r="E78" t="n">
+      <c r="G78" t="n">
         <v>0.08219448005118624</v>
       </c>
-      <c r="F78" t="n">
+      <c r="H78" t="n">
         <v>-0.0006214605893831715</v>
       </c>
-      <c r="G78" t="n">
+      <c r="I78" t="n">
         <v>0.023</v>
       </c>
-      <c r="H78" t="n">
+      <c r="J78" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I78" t="n">
+      <c r="K78" t="n">
         <v>0.1440501534082941</v>
       </c>
-      <c r="J78" t="n">
+      <c r="L78" t="n">
         <v>0.07461163879560084</v>
       </c>
-      <c r="K78" t="n">
+      <c r="M78" t="n">
+        <v>39.04761123835448</v>
+      </c>
+      <c r="N78" t="n">
+        <v>38.95216307515854</v>
+      </c>
+      <c r="O78" t="n">
         <v>39.1320251193151</v>
       </c>
     </row>
@@ -3163,30 +4105,42 @@
         <v>45777</v>
       </c>
       <c r="C79" t="n">
-        <v>0.1052419407702246</v>
+        <v>-0.10198357689549</v>
       </c>
       <c r="D79" t="n">
+        <v>0.07292050156819641</v>
+      </c>
+      <c r="E79" t="n">
+        <v>-0.06151512748202792</v>
+      </c>
+      <c r="F79" t="n">
         <v>0.1112447881360432</v>
       </c>
-      <c r="E79" t="n">
+      <c r="G79" t="n">
         <v>-0.006738165878143465</v>
       </c>
-      <c r="F79" t="n">
+      <c r="H79" t="n">
         <v>0.08219448005118624</v>
       </c>
-      <c r="G79" t="n">
+      <c r="I79" t="n">
         <v>0.023</v>
       </c>
-      <c r="H79" t="n">
+      <c r="J79" t="n">
         <v>0</v>
       </c>
-      <c r="I79" t="n">
+      <c r="K79" t="n">
         <v>0.005823469697138428</v>
       </c>
-      <c r="J79" t="n">
+      <c r="L79" t="n">
         <v>0.1440501534082941</v>
       </c>
-      <c r="K79" t="n">
+      <c r="M79" t="n">
+        <v>41.56356717843155</v>
+      </c>
+      <c r="N79" t="n">
+        <v>39.04761123835448</v>
+      </c>
+      <c r="O79" t="n">
         <v>38.95216307515854</v>
       </c>
     </row>
@@ -3198,30 +4152,42 @@
         <v>45808</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.1772653995221317</v>
+        <v>0.02854557930057244</v>
       </c>
       <c r="D80" t="n">
+        <v>-0.10198357689549</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.0182139556479799</v>
+      </c>
+      <c r="F80" t="n">
         <v>-0.06151512748202792</v>
       </c>
-      <c r="E80" t="n">
+      <c r="G80" t="n">
         <v>0.01665022687424811</v>
       </c>
-      <c r="F80" t="n">
+      <c r="H80" t="n">
         <v>-0.006738165878143465</v>
       </c>
-      <c r="G80" t="n">
+      <c r="I80" t="n">
         <v>0.022</v>
       </c>
-      <c r="H80" t="n">
+      <c r="J80" t="n">
         <v>-0.001000000000000001</v>
       </c>
-      <c r="I80" t="n">
+      <c r="K80" t="n">
         <v>0.02728763762325093</v>
       </c>
-      <c r="J80" t="n">
+      <c r="L80" t="n">
         <v>0.005823469697138428</v>
       </c>
-      <c r="K80" t="n">
+      <c r="M80" t="n">
+        <v>39.89387199635021</v>
+      </c>
+      <c r="N80" t="n">
+        <v>41.56356717843155</v>
+      </c>
+      <c r="O80" t="n">
         <v>39.04761123835448</v>
       </c>
     </row>
@@ -3233,30 +4199,42 @@
         <v>45838</v>
       </c>
       <c r="C81" t="n">
-        <v>0.04609115323664374</v>
+        <v>-0.01505124876527875</v>
       </c>
       <c r="D81" t="n">
+        <v>0.02854557930057244</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.02574691911003146</v>
+      </c>
+      <c r="F81" t="n">
         <v>0.0182139556479799</v>
       </c>
-      <c r="E81" t="n">
+      <c r="G81" t="n">
         <v>0.03575713532400915</v>
       </c>
-      <c r="F81" t="n">
+      <c r="H81" t="n">
         <v>0.01665022687424811</v>
       </c>
-      <c r="G81" t="n">
+      <c r="I81" t="n">
         <v>0.022</v>
       </c>
-      <c r="H81" t="n">
+      <c r="J81" t="n">
         <v>0</v>
       </c>
-      <c r="I81" t="n">
+      <c r="K81" t="n">
         <v>0.03054429876837506</v>
       </c>
-      <c r="J81" t="n">
+      <c r="L81" t="n">
         <v>0.02728763762325093</v>
       </c>
-      <c r="K81" t="n">
+      <c r="M81" t="n">
+        <v>40.50745839325518</v>
+      </c>
+      <c r="N81" t="n">
+        <v>39.89387199635021</v>
+      </c>
+      <c r="O81" t="n">
         <v>41.56356717843155</v>
       </c>
     </row>
@@ -3268,30 +4246,42 @@
         <v>45869</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.02048506337350482</v>
+        <v>0.0469492333303152</v>
       </c>
       <c r="D82" t="n">
+        <v>-0.01505124876527875</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.04891415487853767</v>
+      </c>
+      <c r="F82" t="n">
         <v>0.02574691911003146</v>
       </c>
-      <c r="E82" t="n">
+      <c r="G82" t="n">
         <v>-0.0430383916624697</v>
       </c>
-      <c r="F82" t="n">
+      <c r="H82" t="n">
         <v>0.03575713532400915</v>
       </c>
-      <c r="G82" t="n">
+      <c r="I82" t="n">
         <v>0.022</v>
       </c>
-      <c r="H82" t="n">
+      <c r="J82" t="n">
         <v>0</v>
       </c>
-      <c r="I82" t="n">
+      <c r="K82" t="n">
         <v>0.0855497225337003</v>
       </c>
-      <c r="J82" t="n">
+      <c r="L82" t="n">
         <v>0.03054429876837506</v>
       </c>
-      <c r="K82" t="n">
+      <c r="M82" t="n">
+        <v>40.95003728145939</v>
+      </c>
+      <c r="N82" t="n">
+        <v>40.50745839325518</v>
+      </c>
+      <c r="O82" t="n">
         <v>39.89387199635021</v>
       </c>
     </row>
@@ -3303,30 +4293,42 @@
         <v>45900</v>
       </c>
       <c r="C83" t="n">
-        <v>0.01061257055102657</v>
+        <v>-0.0145690627682229</v>
       </c>
       <c r="D83" t="n">
+        <v>0.0469492333303152</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.05384543273857978</v>
+      </c>
+      <c r="F83" t="n">
         <v>0.04891415487853767</v>
       </c>
-      <c r="E83" t="n">
+      <c r="G83" t="n">
         <v>-0.06108498239471138</v>
       </c>
-      <c r="F83" t="n">
+      <c r="H83" t="n">
         <v>-0.0430383916624697</v>
       </c>
-      <c r="G83" t="n">
+      <c r="I83" t="n">
         <v>0.021</v>
       </c>
-      <c r="H83" t="n">
+      <c r="J83" t="n">
         <v>-0.0009999999999999974</v>
       </c>
-      <c r="I83" t="n">
+      <c r="K83" t="n">
         <v>0.05781588493442591</v>
       </c>
-      <c r="J83" t="n">
+      <c r="L83" t="n">
         <v>0.0855497225337003</v>
       </c>
-      <c r="K83" t="n">
+      <c r="M83" t="n">
+        <v>41.53504180529053</v>
+      </c>
+      <c r="N83" t="n">
+        <v>40.95003728145939</v>
+      </c>
+      <c r="O83" t="n">
         <v>40.50745839325518</v>
       </c>
     </row>
@@ -3338,30 +4340,42 @@
         <v>45930</v>
       </c>
       <c r="C84" t="n">
-        <v>-0.004402244515620551</v>
+        <v>0.02271218046670631</v>
       </c>
       <c r="D84" t="n">
+        <v>-0.0145690627682229</v>
+      </c>
+      <c r="E84" t="n">
+        <v>-0.02749984081238743</v>
+      </c>
+      <c r="F84" t="n">
         <v>0.05384543273857978</v>
       </c>
-      <c r="E84" t="n">
+      <c r="G84" t="n">
         <v>0.03219789047005639</v>
       </c>
-      <c r="F84" t="n">
+      <c r="H84" t="n">
         <v>-0.06108498239471138</v>
       </c>
-      <c r="G84" t="n">
+      <c r="I84" t="n">
         <v>0.022</v>
       </c>
-      <c r="H84" t="n">
+      <c r="J84" t="n">
         <v>0.0009999999999999974</v>
       </c>
-      <c r="I84" t="n">
+      <c r="K84" t="n">
         <v>-0.02065267855087372</v>
       </c>
-      <c r="J84" t="n">
+      <c r="L84" t="n">
         <v>0.05781588493442591</v>
       </c>
-      <c r="K84" t="n">
+      <c r="M84" t="n">
+        <v>42.24944937714299</v>
+      </c>
+      <c r="N84" t="n">
+        <v>41.53504180529053</v>
+      </c>
+      <c r="O84" t="n">
         <v>40.95003728145939</v>
       </c>
     </row>
@@ -3373,30 +4387,42 @@
         <v>45961</v>
       </c>
       <c r="C85" t="n">
-        <v>0.02493596137714947</v>
+        <v>0.07670148505637298</v>
       </c>
       <c r="D85" t="n">
+        <v>0.02271218046670631</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.00774809107558716</v>
+      </c>
+      <c r="F85" t="n">
         <v>-0.02749984081238743</v>
       </c>
-      <c r="E85" t="n">
+      <c r="G85" t="n">
         <v>0.03149181004379042</v>
       </c>
-      <c r="F85" t="n">
+      <c r="H85" t="n">
         <v>0.03219789047005639</v>
       </c>
-      <c r="G85" t="n">
+      <c r="I85" t="n">
         <v>0.022</v>
       </c>
-      <c r="H85" t="n">
+      <c r="J85" t="n">
         <v>0</v>
       </c>
-      <c r="I85" t="n">
+      <c r="K85" t="n">
         <v>0.08677404457608362</v>
       </c>
-      <c r="J85" t="n">
+      <c r="L85" t="n">
         <v>-0.02065267855087372</v>
       </c>
-      <c r="K85" t="n">
+      <c r="M85" t="n">
+        <v>42.60231002324434</v>
+      </c>
+      <c r="N85" t="n">
+        <v>42.24944937714299</v>
+      </c>
+      <c r="O85" t="n">
         <v>41.53504180529053</v>
       </c>
     </row>
@@ -3408,30 +4434,42 @@
         <v>45991</v>
       </c>
       <c r="C86" t="n">
-        <v>0.09476662025233909</v>
+        <v>-0.09857600688087276</v>
       </c>
       <c r="D86" t="n">
+        <v>0.07670148505637298</v>
+      </c>
+      <c r="E86" t="n">
+        <v>-0.01680411715923791</v>
+      </c>
+      <c r="F86" t="n">
         <v>0.00774809107558716</v>
       </c>
-      <c r="E86" t="n">
+      <c r="G86" t="n">
         <v>-0.01930341620925413</v>
       </c>
-      <c r="F86" t="n">
+      <c r="H86" t="n">
         <v>0.03149181004379042</v>
       </c>
-      <c r="G86" t="n">
+      <c r="I86" t="n">
         <v>0.021</v>
       </c>
-      <c r="H86" t="n">
+      <c r="J86" t="n">
         <v>-0.0009999999999999974</v>
       </c>
-      <c r="I86" t="n">
+      <c r="K86" t="n">
         <v>-0.02232536551404041</v>
       </c>
-      <c r="J86" t="n">
+      <c r="L86" t="n">
         <v>0.08677404457608362</v>
       </c>
-      <c r="K86" t="n">
+      <c r="M86" t="n">
+        <v>43.81931756681134</v>
+      </c>
+      <c r="N86" t="n">
+        <v>42.60231002324434</v>
+      </c>
+      <c r="O86" t="n">
         <v>42.24944937714299</v>
       </c>
     </row>
@@ -3443,28 +4481,40 @@
         <v>46022</v>
       </c>
       <c r="C87" t="n">
-        <v>-0.1644907101280775</v>
+        <v>0.1464884265112518</v>
       </c>
       <c r="D87" t="n">
+        <v>-0.09857600688087276</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.1467991800508932</v>
+      </c>
+      <c r="F87" t="n">
         <v>-0.01680411715923791</v>
       </c>
-      <c r="E87" t="inlineStr"/>
-      <c r="F87" t="n">
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="n">
         <v>-0.01930341620925413</v>
       </c>
-      <c r="G87" t="n">
+      <c r="I87" t="n">
         <v>0.022</v>
       </c>
-      <c r="H87" t="n">
+      <c r="J87" t="n">
         <v>0.0009999999999999974</v>
       </c>
-      <c r="I87" t="n">
+      <c r="K87" t="n">
         <v>0.1810699891961254</v>
       </c>
-      <c r="J87" t="n">
+      <c r="L87" t="n">
         <v>-0.02232536551404041</v>
       </c>
-      <c r="K87" t="n">
+      <c r="M87" t="n">
+        <v>42.21743085587008</v>
+      </c>
+      <c r="N87" t="n">
+        <v>43.81931756681134</v>
+      </c>
+      <c r="O87" t="n">
         <v>42.60231002324434</v>
       </c>
     </row>
